--- a/testcase_new/ant测试用例筛选.xlsx
+++ b/testcase_new/ant测试用例筛选.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="203">
   <si>
     <t>用例名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -98,18 +98,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>若按条件查询某条记录的数量少于1或者大于2则表示用例失败（在做并发操作之前预先插入了一条与即将插入的记录相同的记录）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>insert_and_query</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10个线程并发插入100条记录，并发查询记录，待前面的并发操作完成后for循环查找cl中的记录数是否符合预期100条</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>insert_deletes</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -654,10 +646,6 @@
   </si>
   <si>
     <t>metadataconsistency/data/CS11418.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据基本操作相关</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -823,6 +811,26 @@
   </si>
   <si>
     <t>insert_deletecl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程并发插入100条记录，并发查询记录，待前面的并发操作完成后for循环查找cl中的记录数是否符合预期100条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若按条件查询某条记录的数量等于1或者等于2则表示用例失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-11427:插入与查询并发，新增用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> seqDB-11425:并发插入与删除cl并发，新增用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> seqDB-11426:并发插入与删除cs并发，新增用例</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -830,7 +838,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -850,14 +858,6 @@
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -896,7 +896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -905,9 +905,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1217,7 +1214,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="40.5">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1229,7 +1226,7 @@
         <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -1240,7 +1237,7 @@
     </row>
     <row r="2" spans="1:11" ht="40.5">
       <c r="A2" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
@@ -1252,7 +1249,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -1273,7 +1270,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -1294,7 +1291,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1315,7 +1312,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -1324,10 +1321,10 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" ht="27">
+    <row r="6" spans="1:11" ht="54">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>16</v>
@@ -1335,8 +1332,8 @@
       <c r="D6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>160</v>
+      <c r="E6" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -1345,17 +1342,17 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" ht="27">
+    <row r="7" spans="1:11" ht="54">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="4" t="s">
-        <v>160</v>
+      <c r="E7" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -1373,10 +1370,10 @@
         <v>19</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>160</v>
+        <v>199</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -1387,17 +1384,17 @@
     </row>
     <row r="9" spans="1:11" ht="40.5">
       <c r="A9" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>22</v>
+        <v>198</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -1409,13 +1406,13 @@
     <row r="10" spans="1:11" ht="40.5">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -1427,16 +1424,16 @@
     <row r="11" spans="1:11" ht="54">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -1448,14 +1445,14 @@
     <row r="12" spans="1:11" ht="40.5">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -1467,14 +1464,14 @@
     <row r="13" spans="1:11" ht="40.5">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -1486,14 +1483,14 @@
     <row r="14" spans="1:11" ht="40.5">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1504,17 +1501,17 @@
     </row>
     <row r="15" spans="1:11" ht="67.5">
       <c r="A15" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -1526,10 +1523,10 @@
     <row r="16" spans="1:11" ht="27">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1543,10 +1540,10 @@
     <row r="17" spans="1:11" ht="27">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -1560,10 +1557,10 @@
     <row r="18" spans="1:11" ht="27">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -1577,10 +1574,10 @@
     <row r="19" spans="1:11" ht="27">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -1594,10 +1591,10 @@
     <row r="20" spans="1:11" ht="27">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -1611,10 +1608,10 @@
     <row r="21" spans="1:11" ht="27">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -1628,13 +1625,13 @@
     <row r="22" spans="1:11" ht="40.5">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1647,10 +1644,10 @@
     <row r="23" spans="1:11" ht="27">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -1664,10 +1661,10 @@
     <row r="24" spans="1:11" ht="40.5">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -1681,10 +1678,10 @@
     <row r="25" spans="1:11" ht="27">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -1698,10 +1695,10 @@
     <row r="26" spans="1:11" ht="40.5">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -1715,10 +1712,10 @@
     <row r="27" spans="1:11" ht="40.5">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -1731,17 +1728,17 @@
     </row>
     <row r="28" spans="1:11" ht="148.5">
       <c r="A28" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -1753,14 +1750,14 @@
     <row r="29" spans="1:11" ht="54">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -1772,14 +1769,14 @@
     <row r="30" spans="1:11" ht="54">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -1791,14 +1788,14 @@
     <row r="31" spans="1:11" ht="54">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -1810,14 +1807,14 @@
     <row r="32" spans="1:11" ht="54">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -1825,14 +1822,14 @@
     <row r="33" spans="1:7" ht="27">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -1840,14 +1837,14 @@
     <row r="34" spans="1:7" ht="81">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -1855,14 +1852,14 @@
     <row r="35" spans="1:7" ht="94.5">
       <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -1870,14 +1867,14 @@
     <row r="36" spans="1:7" ht="40.5">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -1885,14 +1882,14 @@
     <row r="37" spans="1:7" ht="40.5">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -1900,14 +1897,14 @@
     <row r="38" spans="1:7" ht="54">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -1915,14 +1912,14 @@
     <row r="39" spans="1:7" ht="54">
       <c r="A39" s="1"/>
       <c r="B39" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -1930,14 +1927,14 @@
     <row r="40" spans="1:7" ht="40.5">
       <c r="A40" s="1"/>
       <c r="B40" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -1945,14 +1942,14 @@
     <row r="41" spans="1:7" ht="40.5">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -1960,14 +1957,14 @@
     <row r="42" spans="1:7" ht="40.5">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -1975,14 +1972,14 @@
     <row r="43" spans="1:7" ht="54">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -1990,14 +1987,14 @@
     <row r="44" spans="1:7" ht="54">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -2005,14 +2002,14 @@
     <row r="45" spans="1:7" ht="94.5">
       <c r="A45" s="1"/>
       <c r="B45" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -2020,14 +2017,14 @@
     <row r="46" spans="1:7" ht="54">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -2035,14 +2032,14 @@
     <row r="47" spans="1:7" ht="54">
       <c r="A47" s="1"/>
       <c r="B47" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -2050,14 +2047,14 @@
     <row r="48" spans="1:7" ht="81">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -2065,14 +2062,14 @@
     <row r="49" spans="1:7" ht="54">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -2080,14 +2077,14 @@
     <row r="50" spans="1:7" ht="81">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -2095,14 +2092,14 @@
     <row r="51" spans="1:7" ht="67.5">
       <c r="A51" s="1"/>
       <c r="B51" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -2110,14 +2107,14 @@
     <row r="52" spans="1:7" ht="121.5">
       <c r="A52" s="1"/>
       <c r="B52" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -2125,14 +2122,14 @@
     <row r="53" spans="1:7" ht="94.5">
       <c r="A53" s="1"/>
       <c r="B53" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -2140,14 +2137,14 @@
     <row r="54" spans="1:7" ht="40.5">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -2155,14 +2152,14 @@
     <row r="55" spans="1:7" ht="54">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -2170,14 +2167,14 @@
     <row r="56" spans="1:7" ht="81">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -2185,14 +2182,14 @@
     <row r="57" spans="1:7" ht="67.5">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -2200,14 +2197,14 @@
     <row r="58" spans="1:7" ht="27">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -2215,14 +2212,14 @@
     <row r="59" spans="1:7" ht="27">
       <c r="A59" s="1"/>
       <c r="B59" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -2230,31 +2227,31 @@
     <row r="60" spans="1:7" ht="54">
       <c r="A60" s="1"/>
       <c r="B60" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" ht="27">
       <c r="A61" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -2262,14 +2259,14 @@
     <row r="62" spans="1:7" ht="27">
       <c r="A62" s="1"/>
       <c r="B62" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -2277,14 +2274,14 @@
     <row r="63" spans="1:7" ht="40.5">
       <c r="A63" s="1"/>
       <c r="B63" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -2292,14 +2289,14 @@
     <row r="64" spans="1:7" ht="27">
       <c r="A64" s="1"/>
       <c r="B64" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -2307,16 +2304,16 @@
     <row r="65" spans="1:7" ht="27">
       <c r="A65" s="1"/>
       <c r="B65" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="D65" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -2324,14 +2321,14 @@
     <row r="66" spans="1:7" ht="40.5">
       <c r="A66" s="1"/>
       <c r="B66" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D66" s="1"/>
       <c r="E66" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
@@ -2339,16 +2336,16 @@
     <row r="67" spans="1:7" ht="27">
       <c r="A67" s="1"/>
       <c r="B67" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="E67" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
@@ -2356,33 +2353,33 @@
     <row r="68" spans="1:7" ht="27">
       <c r="A68" s="1"/>
       <c r="B68" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
     <row r="69" spans="1:7" ht="27">
       <c r="A69" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>

--- a/testcase_new/ant测试用例筛选.xlsx
+++ b/testcase_new/ant测试用例筛选.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="206">
   <si>
     <t>用例名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -90,14 +90,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>insert_query</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10个线程做插入操作，10个线程做查询操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>insert_and_query</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -593,10 +585,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>export_data（黄晓妮）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>import_data（黄晓妮）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -650,11 +638,6 @@
   </si>
   <si>
     <t>导出工具未测试，用例需要保留，后续补充该story测试时再做筛选</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无用例（导入工具之前主要是针对CSV文件格式做的测试，json格式需要补充）
-补充手工用例： seqDB-11421:导入导出数据（覆盖所有数据类型）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -818,6 +801,30 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve"> seqDB-11426:并发插入与删除cs并发，新增用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>export_data（黄晓妮）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> seqDB-11425:并发插入与删除cl并发，新增用例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已补充</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insert_query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个线程做插入操作，10个线程做查询操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>若按条件查询某条记录的数量等于1或者等于2则表示用例失败</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -826,11 +833,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> seqDB-11425:并发插入与删除cl并发，新增用例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> seqDB-11426:并发插入与删除cs并发，新增用例</t>
+    <t>无用例（导入工具之前主要是针对CSV文件格式做的测试，json格式需要补充）
+补充手工用例： seqDB-11421:导入导出数据（覆盖所有数据类型）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与1541重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已重新设计并自动化上CI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -838,7 +850,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -860,13 +872,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -896,7 +927,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -907,6 +938,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1214,7 +1252,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="40.5">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1226,7 +1264,7 @@
         <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -1237,7 +1275,7 @@
     </row>
     <row r="2" spans="1:11" ht="40.5">
       <c r="A2" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
@@ -1249,7 +1287,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -1270,7 +1308,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -1291,7 +1329,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1312,7 +1350,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -1324,7 +1362,7 @@
     <row r="6" spans="1:11" ht="54">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>16</v>
@@ -1333,9 +1371,11 @@
         <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="1"/>
+        <v>197</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -1345,58 +1385,64 @@
     <row r="7" spans="1:11" ht="54">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F7" s="1"/>
+        <v>195</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" ht="40.5">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="1" t="s">
+    <row r="8" spans="1:11" s="6" customFormat="1" ht="40.5">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="C8" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+      <c r="D8" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
     </row>
     <row r="9" spans="1:11" ht="40.5">
       <c r="A9" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="F9" s="1"/>
+        <v>147</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -1406,15 +1452,17 @@
     <row r="10" spans="1:11" ht="40.5">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F10" s="1"/>
+        <v>148</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1424,18 +1472,20 @@
     <row r="11" spans="1:11" ht="54">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F11" s="1"/>
+        <v>149</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1445,16 +1495,18 @@
     <row r="12" spans="1:11" ht="40.5">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="F12" s="1"/>
+        <v>147</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -1464,16 +1516,18 @@
     <row r="13" spans="1:11" ht="40.5">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F13" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1483,16 +1537,18 @@
     <row r="14" spans="1:11" ht="40.5">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F14" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -1501,19 +1557,21 @@
     </row>
     <row r="15" spans="1:11" ht="67.5">
       <c r="A15" s="1" t="s">
-        <v>144</v>
+        <v>196</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F15" s="1"/>
+        <v>155</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>205</v>
+      </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1523,10 +1581,10 @@
     <row r="16" spans="1:11" ht="27">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1540,10 +1598,10 @@
     <row r="17" spans="1:11" ht="27">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -1557,10 +1615,10 @@
     <row r="18" spans="1:11" ht="27">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -1574,10 +1632,10 @@
     <row r="19" spans="1:11" ht="27">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -1591,10 +1649,10 @@
     <row r="20" spans="1:11" ht="27">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -1608,10 +1666,10 @@
     <row r="21" spans="1:11" ht="27">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -1625,13 +1683,13 @@
     <row r="22" spans="1:11" ht="40.5">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1644,10 +1702,10 @@
     <row r="23" spans="1:11" ht="27">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -1661,10 +1719,10 @@
     <row r="24" spans="1:11" ht="40.5">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -1678,10 +1736,10 @@
     <row r="25" spans="1:11" ht="27">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -1695,10 +1753,10 @@
     <row r="26" spans="1:11" ht="40.5">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -1712,10 +1770,10 @@
     <row r="27" spans="1:11" ht="40.5">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -1728,17 +1786,17 @@
     </row>
     <row r="28" spans="1:11" ht="148.5">
       <c r="A28" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -1750,14 +1808,14 @@
     <row r="29" spans="1:11" ht="54">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -1769,14 +1827,14 @@
     <row r="30" spans="1:11" ht="54">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -1788,14 +1846,14 @@
     <row r="31" spans="1:11" ht="54">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -1807,14 +1865,14 @@
     <row r="32" spans="1:11" ht="54">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -1822,14 +1880,14 @@
     <row r="33" spans="1:7" ht="27">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -1837,14 +1895,14 @@
     <row r="34" spans="1:7" ht="81">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -1852,14 +1910,14 @@
     <row r="35" spans="1:7" ht="94.5">
       <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -1867,14 +1925,14 @@
     <row r="36" spans="1:7" ht="40.5">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -1882,14 +1940,14 @@
     <row r="37" spans="1:7" ht="40.5">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -1897,14 +1955,14 @@
     <row r="38" spans="1:7" ht="54">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -1912,14 +1970,14 @@
     <row r="39" spans="1:7" ht="54">
       <c r="A39" s="1"/>
       <c r="B39" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -1927,14 +1985,14 @@
     <row r="40" spans="1:7" ht="40.5">
       <c r="A40" s="1"/>
       <c r="B40" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -1942,14 +2000,14 @@
     <row r="41" spans="1:7" ht="40.5">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -1957,14 +2015,14 @@
     <row r="42" spans="1:7" ht="40.5">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -1972,14 +2030,14 @@
     <row r="43" spans="1:7" ht="54">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -1987,14 +2045,14 @@
     <row r="44" spans="1:7" ht="54">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -2002,14 +2060,14 @@
     <row r="45" spans="1:7" ht="94.5">
       <c r="A45" s="1"/>
       <c r="B45" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -2017,14 +2075,14 @@
     <row r="46" spans="1:7" ht="54">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -2032,14 +2090,14 @@
     <row r="47" spans="1:7" ht="54">
       <c r="A47" s="1"/>
       <c r="B47" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -2047,14 +2105,14 @@
     <row r="48" spans="1:7" ht="81">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -2062,14 +2120,14 @@
     <row r="49" spans="1:7" ht="54">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -2077,14 +2135,14 @@
     <row r="50" spans="1:7" ht="81">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -2092,14 +2150,14 @@
     <row r="51" spans="1:7" ht="67.5">
       <c r="A51" s="1"/>
       <c r="B51" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -2107,14 +2165,14 @@
     <row r="52" spans="1:7" ht="121.5">
       <c r="A52" s="1"/>
       <c r="B52" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -2122,14 +2180,14 @@
     <row r="53" spans="1:7" ht="94.5">
       <c r="A53" s="1"/>
       <c r="B53" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -2137,14 +2195,14 @@
     <row r="54" spans="1:7" ht="40.5">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -2152,14 +2210,14 @@
     <row r="55" spans="1:7" ht="54">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -2167,14 +2225,14 @@
     <row r="56" spans="1:7" ht="81">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -2182,14 +2240,14 @@
     <row r="57" spans="1:7" ht="67.5">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -2197,14 +2255,14 @@
     <row r="58" spans="1:7" ht="27">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -2212,14 +2270,14 @@
     <row r="59" spans="1:7" ht="27">
       <c r="A59" s="1"/>
       <c r="B59" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -2227,159 +2285,175 @@
     <row r="60" spans="1:7" ht="54">
       <c r="A60" s="1"/>
       <c r="B60" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" ht="27">
       <c r="A61" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F61" s="1"/>
+        <v>180</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" ht="27">
       <c r="A62" s="1"/>
       <c r="B62" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F62" s="1"/>
+        <v>181</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" ht="40.5">
       <c r="A63" s="1"/>
       <c r="B63" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F63" s="1"/>
+        <v>182</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G63" s="1"/>
     </row>
     <row r="64" spans="1:7" ht="27">
       <c r="A64" s="1"/>
       <c r="B64" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F64" s="1"/>
+        <v>183</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" ht="27">
       <c r="A65" s="1"/>
       <c r="B65" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="D65" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F65" s="1"/>
+        <v>184</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G65" s="1"/>
     </row>
     <row r="66" spans="1:7" ht="40.5">
       <c r="A66" s="1"/>
       <c r="B66" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D66" s="1"/>
       <c r="E66" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F66" s="1"/>
+        <v>185</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="1:7" ht="27">
       <c r="A67" s="1"/>
       <c r="B67" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="E67" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F67" s="1"/>
+        <v>186</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G67" s="1"/>
     </row>
     <row r="68" spans="1:7" ht="27">
       <c r="A68" s="1"/>
       <c r="B68" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F68" s="1"/>
+        <v>187</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="G68" s="1"/>
     </row>
     <row r="69" spans="1:7" ht="27">
       <c r="A69" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
